--- a/output/yearly_population_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_11_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8537</v>
+        <v>5023</v>
       </c>
       <c r="C2" t="n">
-        <v>3702</v>
+        <v>11232</v>
       </c>
       <c r="D2" t="n">
-        <v>20100</v>
+        <v>20631</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5059</v>
+        <v>3288</v>
       </c>
       <c r="C3" t="n">
-        <v>3063</v>
+        <v>5008</v>
       </c>
       <c r="D3" t="n">
-        <v>10751</v>
+        <v>14632</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4110</v>
+        <v>2635</v>
       </c>
       <c r="C4" t="n">
-        <v>3805</v>
+        <v>6733</v>
       </c>
       <c r="D4" t="n">
-        <v>5252</v>
+        <v>7657</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2593</v>
+        <v>1634</v>
       </c>
       <c r="C5" t="n">
-        <v>3114</v>
+        <v>6311</v>
       </c>
       <c r="D5" t="n">
-        <v>2228</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1373</v>
+        <v>919</v>
       </c>
       <c r="C6" t="n">
-        <v>2165</v>
+        <v>4281</v>
       </c>
       <c r="D6" t="n">
-        <v>1071</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>631</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>1483</v>
+        <v>2596</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>242</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>797</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>473</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -996,7 +996,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10313</v>
+        <v>6102</v>
       </c>
       <c r="C2" t="n">
-        <v>4042</v>
+        <v>10986</v>
       </c>
       <c r="D2" t="n">
-        <v>21712</v>
+        <v>26846</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5393</v>
+        <v>3276</v>
       </c>
       <c r="C3" t="n">
-        <v>2951</v>
+        <v>6771</v>
       </c>
       <c r="D3" t="n">
-        <v>11357</v>
+        <v>14440</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3884</v>
+        <v>2484</v>
       </c>
       <c r="C4" t="n">
-        <v>3355</v>
+        <v>5814</v>
       </c>
       <c r="D4" t="n">
-        <v>6042</v>
+        <v>8495</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2884</v>
+        <v>1819</v>
       </c>
       <c r="C5" t="n">
-        <v>3351</v>
+        <v>6301</v>
       </c>
       <c r="D5" t="n">
-        <v>2632</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1756</v>
+        <v>1095</v>
       </c>
       <c r="C6" t="n">
-        <v>2589</v>
+        <v>5099</v>
       </c>
       <c r="D6" t="n">
-        <v>1245</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="7">
@@ -1161,10 +1161,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>856</v>
+        <v>567</v>
       </c>
       <c r="C7" t="n">
-        <v>1782</v>
+        <v>3263</v>
       </c>
       <c r="D7" t="n">
         <v>700</v>
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>362</v>
+        <v>241</v>
       </c>
       <c r="C8" t="n">
-        <v>1105</v>
+        <v>1759</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>547</v>
+        <v>764</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12749</v>
+        <v>5970</v>
       </c>
       <c r="C2" t="n">
-        <v>5090</v>
+        <v>15775</v>
       </c>
       <c r="D2" t="n">
-        <v>27764</v>
+        <v>24506</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6057</v>
+        <v>3522</v>
       </c>
       <c r="C3" t="n">
-        <v>3025</v>
+        <v>7461</v>
       </c>
       <c r="D3" t="n">
-        <v>11937</v>
+        <v>14928</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3856</v>
+        <v>2373</v>
       </c>
       <c r="C4" t="n">
-        <v>3066</v>
+        <v>6023</v>
       </c>
       <c r="D4" t="n">
-        <v>6616</v>
+        <v>8954</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2969</v>
+        <v>1845</v>
       </c>
       <c r="C5" t="n">
-        <v>3283</v>
+        <v>5917</v>
       </c>
       <c r="D5" t="n">
-        <v>3075</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>1242</v>
       </c>
       <c r="C6" t="n">
-        <v>2868</v>
+        <v>5517</v>
       </c>
       <c r="D6" t="n">
-        <v>1416</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1098</v>
+        <v>685</v>
       </c>
       <c r="C7" t="n">
-        <v>2129</v>
+        <v>3913</v>
       </c>
       <c r="D7" t="n">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>497</v>
+        <v>318</v>
       </c>
       <c r="C8" t="n">
-        <v>1372</v>
+        <v>2286</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>196</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>770</v>
+        <v>1107</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>378</v>
+        <v>468</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D12" t="n">
         <v>163</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11403</v>
+        <v>5622</v>
       </c>
       <c r="C2" t="n">
-        <v>3339</v>
+        <v>11105</v>
       </c>
       <c r="D2" t="n">
-        <v>22447</v>
+        <v>20464</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7258</v>
+        <v>4182</v>
       </c>
       <c r="C3" t="n">
-        <v>4814</v>
+        <v>11336</v>
       </c>
       <c r="D3" t="n">
-        <v>13192</v>
+        <v>16307</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2743</v>
+        <v>1704</v>
       </c>
       <c r="C4" t="n">
-        <v>4917</v>
+        <v>8802</v>
       </c>
       <c r="D4" t="n">
-        <v>6478</v>
+        <v>8568</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1870</v>
+        <v>1147</v>
       </c>
       <c r="C5" t="n">
-        <v>2810</v>
+        <v>5406</v>
       </c>
       <c r="D5" t="n">
-        <v>2243</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1014</v>
+        <v>632</v>
       </c>
       <c r="C6" t="n">
-        <v>2086</v>
+        <v>3834</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>459</v>
+        <v>293</v>
       </c>
       <c r="C7" t="n">
-        <v>1344</v>
+        <v>2240</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>754</v>
+        <v>1084</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>458</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
         <v>159</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6918</v>
+        <v>3491</v>
       </c>
       <c r="C2" t="n">
-        <v>1876</v>
+        <v>5229</v>
       </c>
       <c r="D2" t="n">
-        <v>15463</v>
+        <v>15441</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7789</v>
+        <v>4131</v>
       </c>
       <c r="C3" t="n">
-        <v>3706</v>
+        <v>10229</v>
       </c>
       <c r="D3" t="n">
-        <v>13870</v>
+        <v>15925</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3932</v>
+        <v>2258</v>
       </c>
       <c r="C4" t="n">
-        <v>4953</v>
+        <v>10075</v>
       </c>
       <c r="D4" t="n">
-        <v>7374</v>
+        <v>9586</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2099</v>
+        <v>1277</v>
       </c>
       <c r="C5" t="n">
-        <v>3796</v>
+        <v>6805</v>
       </c>
       <c r="D5" t="n">
-        <v>2787</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1224</v>
+        <v>735</v>
       </c>
       <c r="C6" t="n">
-        <v>2456</v>
+        <v>4582</v>
       </c>
       <c r="D6" t="n">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>448</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>1680</v>
+        <v>2805</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>962</v>
+        <v>1425</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7841</v>
+        <v>3366</v>
       </c>
       <c r="C2" t="n">
-        <v>9836</v>
+        <v>7248</v>
       </c>
       <c r="D2" t="n">
-        <v>15536</v>
+        <v>15154</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6206</v>
+        <v>3264</v>
       </c>
       <c r="C3" t="n">
-        <v>2462</v>
+        <v>7057</v>
       </c>
       <c r="D3" t="n">
-        <v>13268</v>
+        <v>14941</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4896</v>
+        <v>2584</v>
       </c>
       <c r="C4" t="n">
-        <v>4203</v>
+        <v>10034</v>
       </c>
       <c r="D4" t="n">
-        <v>8272</v>
+        <v>10268</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2576</v>
+        <v>1490</v>
       </c>
       <c r="C5" t="n">
-        <v>4294</v>
+        <v>8107</v>
       </c>
       <c r="D5" t="n">
-        <v>3450</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1472</v>
+        <v>869</v>
       </c>
       <c r="C6" t="n">
-        <v>3097</v>
+        <v>5478</v>
       </c>
       <c r="D6" t="n">
-        <v>1198</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>681</v>
+        <v>394</v>
       </c>
       <c r="C7" t="n">
-        <v>2053</v>
+        <v>3562</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>228</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>1280</v>
+        <v>1965</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>817</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4535</v>
+        <v>2037</v>
       </c>
       <c r="C2" t="n">
-        <v>4283</v>
+        <v>3569</v>
       </c>
       <c r="D2" t="n">
-        <v>10628</v>
+        <v>10703</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6395</v>
+        <v>3202</v>
       </c>
       <c r="C3" t="n">
-        <v>5085</v>
+        <v>6935</v>
       </c>
       <c r="D3" t="n">
-        <v>13200</v>
+        <v>14650</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5474</v>
+        <v>2810</v>
       </c>
       <c r="C4" t="n">
-        <v>3924</v>
+        <v>9902</v>
       </c>
       <c r="D4" t="n">
-        <v>9024</v>
+        <v>10885</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2696</v>
+        <v>1539</v>
       </c>
       <c r="C5" t="n">
-        <v>4820</v>
+        <v>9808</v>
       </c>
       <c r="D5" t="n">
-        <v>3747</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1268</v>
+        <v>701</v>
       </c>
       <c r="C6" t="n">
-        <v>3928</v>
+        <v>6394</v>
       </c>
       <c r="D6" t="n">
-        <v>1192</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>2256</v>
+        <v>3636</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1068</v>
+        <v>1359</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5706</v>
+        <v>2415</v>
       </c>
       <c r="C2" t="n">
-        <v>3689</v>
+        <v>7626</v>
       </c>
       <c r="D2" t="n">
-        <v>14289</v>
+        <v>14869</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4756</v>
+        <v>2354</v>
       </c>
       <c r="C3" t="n">
-        <v>4144</v>
+        <v>4899</v>
       </c>
       <c r="D3" t="n">
-        <v>11921</v>
+        <v>13183</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5133</v>
+        <v>2589</v>
       </c>
       <c r="C4" t="n">
-        <v>4470</v>
+        <v>8452</v>
       </c>
       <c r="D4" t="n">
-        <v>9471</v>
+        <v>11132</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3438</v>
+        <v>1809</v>
       </c>
       <c r="C5" t="n">
-        <v>4335</v>
+        <v>9643</v>
       </c>
       <c r="D5" t="n">
-        <v>4530</v>
+        <v>5029</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1692</v>
+        <v>912</v>
       </c>
       <c r="C6" t="n">
-        <v>4330</v>
+        <v>7839</v>
       </c>
       <c r="D6" t="n">
-        <v>1544</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>498</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>3020</v>
+        <v>4697</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1554</v>
+        <v>2166</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>585</v>
+        <v>636</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4314</v>
+        <v>1660</v>
       </c>
       <c r="C2" t="n">
-        <v>2853</v>
+        <v>4433</v>
       </c>
       <c r="D2" t="n">
-        <v>10634</v>
+        <v>10808</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4449</v>
+        <v>2081</v>
       </c>
       <c r="C3" t="n">
-        <v>3594</v>
+        <v>5384</v>
       </c>
       <c r="D3" t="n">
-        <v>11556</v>
+        <v>12675</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4573</v>
+        <v>2326</v>
       </c>
       <c r="C4" t="n">
-        <v>4361</v>
+        <v>7155</v>
       </c>
       <c r="D4" t="n">
-        <v>9626</v>
+        <v>11156</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3805</v>
+        <v>1928</v>
       </c>
       <c r="C5" t="n">
-        <v>4464</v>
+        <v>9412</v>
       </c>
       <c r="D5" t="n">
-        <v>5095</v>
+        <v>5617</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2047</v>
+        <v>1050</v>
       </c>
       <c r="C6" t="n">
-        <v>4511</v>
+        <v>8676</v>
       </c>
       <c r="D6" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>3585</v>
+        <v>5648</v>
       </c>
       <c r="D7" t="n">
-        <v>755</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1969</v>
+        <v>2768</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>732</v>
+        <v>673</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7491</v>
+        <v>2372</v>
       </c>
       <c r="C2" t="n">
-        <v>5242</v>
+        <v>9055</v>
       </c>
       <c r="D2" t="n">
-        <v>19726</v>
+        <v>16333</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3692</v>
+        <v>1634</v>
       </c>
       <c r="C3" t="n">
-        <v>2912</v>
+        <v>4538</v>
       </c>
       <c r="D3" t="n">
-        <v>10679</v>
+        <v>11674</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3932</v>
+        <v>1970</v>
       </c>
       <c r="C4" t="n">
-        <v>3916</v>
+        <v>6240</v>
       </c>
       <c r="D4" t="n">
-        <v>9629</v>
+        <v>11021</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3762</v>
+        <v>1879</v>
       </c>
       <c r="C5" t="n">
-        <v>4325</v>
+        <v>8349</v>
       </c>
       <c r="D5" t="n">
-        <v>5543</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2500</v>
+        <v>1234</v>
       </c>
       <c r="C6" t="n">
-        <v>4449</v>
+        <v>8875</v>
       </c>
       <c r="D6" t="n">
-        <v>2286</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>922</v>
+        <v>414</v>
       </c>
       <c r="C7" t="n">
-        <v>3999</v>
+        <v>6769</v>
       </c>
       <c r="D7" t="n">
-        <v>896</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>2585</v>
+        <v>3698</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1187</v>
+        <v>1315</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="D10" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8555</v>
+        <v>5978</v>
       </c>
       <c r="C2" t="n">
-        <v>6399</v>
+        <v>13761</v>
       </c>
       <c r="D2" t="n">
-        <v>9077</v>
+        <v>11219</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5188</v>
+        <v>1751</v>
       </c>
       <c r="C2" t="n">
-        <v>2851</v>
+        <v>5361</v>
       </c>
       <c r="D2" t="n">
-        <v>14360</v>
+        <v>12151</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5123</v>
+        <v>2215</v>
       </c>
       <c r="C3" t="n">
-        <v>3746</v>
+        <v>6011</v>
       </c>
       <c r="D3" t="n">
-        <v>12226</v>
+        <v>12968</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5478</v>
+        <v>2743</v>
       </c>
       <c r="C4" t="n">
-        <v>5354</v>
+        <v>9024</v>
       </c>
       <c r="D4" t="n">
-        <v>9913</v>
+        <v>11252</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2518</v>
+        <v>1140</v>
       </c>
       <c r="C5" t="n">
-        <v>6305</v>
+        <v>12428</v>
       </c>
       <c r="D5" t="n">
-        <v>5195</v>
+        <v>5465</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>382</v>
       </c>
       <c r="C6" t="n">
-        <v>4921</v>
+        <v>8112</v>
       </c>
       <c r="D6" t="n">
-        <v>1897</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>2533</v>
+        <v>3624</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1163</v>
+        <v>1288</v>
       </c>
       <c r="D8" t="n">
-        <v>309</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>401</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="D10" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7969</v>
+        <v>6512</v>
       </c>
       <c r="C2" t="n">
-        <v>5419</v>
+        <v>6360</v>
       </c>
       <c r="D2" t="n">
-        <v>11710</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3632</v>
+        <v>2540</v>
       </c>
       <c r="C3" t="n">
-        <v>3225</v>
+        <v>6935</v>
       </c>
       <c r="D3" t="n">
-        <v>2164</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>4735</v>
       </c>
       <c r="C2" t="n">
-        <v>4013</v>
+        <v>10759</v>
       </c>
       <c r="D2" t="n">
-        <v>15200</v>
+        <v>22032</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4767</v>
+        <v>3717</v>
       </c>
       <c r="C3" t="n">
-        <v>3851</v>
+        <v>5700</v>
       </c>
       <c r="D3" t="n">
-        <v>3608</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1611</v>
+        <v>1138</v>
       </c>
       <c r="C4" t="n">
-        <v>1933</v>
+        <v>4107</v>
       </c>
       <c r="D4" t="n">
-        <v>1617</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6471</v>
+        <v>4269</v>
       </c>
       <c r="C2" t="n">
-        <v>2927</v>
+        <v>7313</v>
       </c>
       <c r="D2" t="n">
-        <v>16532</v>
+        <v>30846</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4099</v>
+        <v>3465</v>
       </c>
       <c r="C3" t="n">
-        <v>3409</v>
+        <v>7290</v>
       </c>
       <c r="D3" t="n">
-        <v>5202</v>
+        <v>6995</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2703</v>
+        <v>2033</v>
       </c>
       <c r="C4" t="n">
-        <v>2979</v>
+        <v>4908</v>
       </c>
       <c r="D4" t="n">
-        <v>1950</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>721</v>
+        <v>519</v>
       </c>
       <c r="C5" t="n">
-        <v>1153</v>
+        <v>2305</v>
       </c>
       <c r="D5" t="n">
-        <v>1217</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>371</v>
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8822</v>
+        <v>5111</v>
       </c>
       <c r="C2" t="n">
-        <v>5203</v>
+        <v>13231</v>
       </c>
       <c r="D2" t="n">
-        <v>19102</v>
+        <v>28875</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4284</v>
+        <v>3165</v>
       </c>
       <c r="C3" t="n">
-        <v>2751</v>
+        <v>6367</v>
       </c>
       <c r="D3" t="n">
-        <v>6557</v>
+        <v>10127</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2908</v>
+        <v>2327</v>
       </c>
       <c r="C4" t="n">
-        <v>3119</v>
+        <v>6063</v>
       </c>
       <c r="D4" t="n">
-        <v>2465</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1409</v>
+        <v>1035</v>
       </c>
       <c r="C5" t="n">
-        <v>2093</v>
+        <v>3581</v>
       </c>
       <c r="D5" t="n">
-        <v>1313</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>731</v>
+        <v>1277</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10219</v>
+        <v>6605</v>
       </c>
       <c r="C2" t="n">
-        <v>6835</v>
+        <v>11385</v>
       </c>
       <c r="D2" t="n">
-        <v>18182</v>
+        <v>33645</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4738</v>
+        <v>2967</v>
       </c>
       <c r="C3" t="n">
-        <v>3297</v>
+        <v>7988</v>
       </c>
       <c r="D3" t="n">
-        <v>7528</v>
+        <v>11398</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2247</v>
+        <v>1698</v>
       </c>
       <c r="C4" t="n">
-        <v>2388</v>
+        <v>5040</v>
       </c>
       <c r="D4" t="n">
-        <v>2715</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1130</v>
+        <v>861</v>
       </c>
       <c r="C5" t="n">
-        <v>1924</v>
+        <v>3533</v>
       </c>
       <c r="D5" t="n">
-        <v>1202</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>424</v>
+        <v>306</v>
       </c>
       <c r="C6" t="n">
-        <v>950</v>
+        <v>1602</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>345</v>
+        <v>508</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7234</v>
+        <v>5202</v>
       </c>
       <c r="C2" t="n">
-        <v>4515</v>
+        <v>6150</v>
       </c>
       <c r="D2" t="n">
-        <v>16227</v>
+        <v>24251</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6271</v>
+        <v>3933</v>
       </c>
       <c r="C3" t="n">
-        <v>4638</v>
+        <v>8546</v>
       </c>
       <c r="D3" t="n">
-        <v>8836</v>
+        <v>14296</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3098</v>
+        <v>2027</v>
       </c>
       <c r="C4" t="n">
-        <v>2896</v>
+        <v>6661</v>
       </c>
       <c r="D4" t="n">
-        <v>3648</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1517</v>
+        <v>1122</v>
       </c>
       <c r="C5" t="n">
-        <v>2141</v>
+        <v>4313</v>
       </c>
       <c r="D5" t="n">
-        <v>1470</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>721</v>
+        <v>534</v>
       </c>
       <c r="C6" t="n">
-        <v>1508</v>
+        <v>2624</v>
       </c>
       <c r="D6" t="n">
-        <v>830</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>694</v>
+        <v>1108</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>290</v>
+        <v>373</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>197</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6773</v>
+        <v>4291</v>
       </c>
       <c r="C2" t="n">
-        <v>3116</v>
+        <v>4937</v>
       </c>
       <c r="D2" t="n">
-        <v>22734</v>
+        <v>20871</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5565</v>
+        <v>3731</v>
       </c>
       <c r="C3" t="n">
-        <v>3948</v>
+        <v>6365</v>
       </c>
       <c r="D3" t="n">
-        <v>9382</v>
+        <v>14802</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4017</v>
+        <v>2524</v>
       </c>
       <c r="C4" t="n">
-        <v>3811</v>
+        <v>7535</v>
       </c>
       <c r="D4" t="n">
-        <v>4498</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2036</v>
+        <v>1357</v>
       </c>
       <c r="C5" t="n">
-        <v>2524</v>
+        <v>5399</v>
       </c>
       <c r="D5" t="n">
-        <v>1843</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1018</v>
+        <v>742</v>
       </c>
       <c r="C6" t="n">
-        <v>1836</v>
+        <v>3454</v>
       </c>
       <c r="D6" t="n">
-        <v>926</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>303</v>
       </c>
       <c r="C7" t="n">
-        <v>1132</v>
+        <v>1865</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>499</v>
+        <v>722</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_11_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5023</v>
+        <v>7198</v>
       </c>
       <c r="C2" t="n">
-        <v>11232</v>
+        <v>3478</v>
       </c>
       <c r="D2" t="n">
-        <v>20631</v>
+        <v>30617</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3288</v>
+        <v>5133</v>
       </c>
       <c r="C3" t="n">
-        <v>5008</v>
+        <v>2433</v>
       </c>
       <c r="D3" t="n">
-        <v>14632</v>
+        <v>18470</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2635</v>
+        <v>3799</v>
       </c>
       <c r="C4" t="n">
-        <v>6733</v>
+        <v>2991</v>
       </c>
       <c r="D4" t="n">
-        <v>7657</v>
+        <v>8084</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1634</v>
+        <v>2411</v>
       </c>
       <c r="C5" t="n">
-        <v>6311</v>
+        <v>2987</v>
       </c>
       <c r="D5" t="n">
-        <v>2855</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>919</v>
+        <v>1355</v>
       </c>
       <c r="C6" t="n">
-        <v>4281</v>
+        <v>2630</v>
       </c>
       <c r="D6" t="n">
-        <v>1141</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>619</v>
       </c>
       <c r="C7" t="n">
-        <v>2596</v>
+        <v>2010</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="C8" t="n">
-        <v>1218</v>
+        <v>1091</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6102</v>
+        <v>10583</v>
       </c>
       <c r="C2" t="n">
-        <v>10986</v>
+        <v>6373</v>
       </c>
       <c r="D2" t="n">
-        <v>26846</v>
+        <v>29979</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3276</v>
+        <v>4941</v>
       </c>
       <c r="C3" t="n">
-        <v>6771</v>
+        <v>2554</v>
       </c>
       <c r="D3" t="n">
-        <v>14440</v>
+        <v>18880</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2484</v>
+        <v>3735</v>
       </c>
       <c r="C4" t="n">
-        <v>5814</v>
+        <v>2637</v>
       </c>
       <c r="D4" t="n">
-        <v>8495</v>
+        <v>9533</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1819</v>
+        <v>2675</v>
       </c>
       <c r="C5" t="n">
-        <v>6301</v>
+        <v>2926</v>
       </c>
       <c r="D5" t="n">
-        <v>3432</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1095</v>
+        <v>1635</v>
       </c>
       <c r="C6" t="n">
-        <v>5099</v>
+        <v>2736</v>
       </c>
       <c r="D6" t="n">
-        <v>1372</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>567</v>
+        <v>829</v>
       </c>
       <c r="C7" t="n">
-        <v>3263</v>
+        <v>2282</v>
       </c>
       <c r="D7" t="n">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>341</v>
       </c>
       <c r="C8" t="n">
-        <v>1759</v>
+        <v>1467</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C9" t="n">
-        <v>764</v>
+        <v>709</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5970</v>
+        <v>12475</v>
       </c>
       <c r="C2" t="n">
-        <v>15775</v>
+        <v>4673</v>
       </c>
       <c r="D2" t="n">
-        <v>24506</v>
+        <v>38906</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3522</v>
+        <v>5827</v>
       </c>
       <c r="C3" t="n">
-        <v>7461</v>
+        <v>3642</v>
       </c>
       <c r="D3" t="n">
-        <v>14928</v>
+        <v>19003</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2373</v>
+        <v>3604</v>
       </c>
       <c r="C4" t="n">
-        <v>6023</v>
+        <v>2520</v>
       </c>
       <c r="D4" t="n">
-        <v>8954</v>
+        <v>10497</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1845</v>
+        <v>2784</v>
       </c>
       <c r="C5" t="n">
-        <v>5917</v>
+        <v>2714</v>
       </c>
       <c r="D5" t="n">
-        <v>4008</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1242</v>
+        <v>1862</v>
       </c>
       <c r="C6" t="n">
-        <v>5517</v>
+        <v>2789</v>
       </c>
       <c r="D6" t="n">
-        <v>1598</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>685</v>
+        <v>1026</v>
       </c>
       <c r="C7" t="n">
-        <v>3913</v>
+        <v>2441</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>318</v>
+        <v>467</v>
       </c>
       <c r="C8" t="n">
-        <v>2286</v>
+        <v>1771</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="C9" t="n">
-        <v>1107</v>
+        <v>998</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5622</v>
+        <v>11235</v>
       </c>
       <c r="C2" t="n">
-        <v>11105</v>
+        <v>3177</v>
       </c>
       <c r="D2" t="n">
-        <v>20464</v>
+        <v>31854</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4182</v>
+        <v>6794</v>
       </c>
       <c r="C3" t="n">
-        <v>11336</v>
+        <v>5073</v>
       </c>
       <c r="D3" t="n">
-        <v>16307</v>
+        <v>20737</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1704</v>
+        <v>2572</v>
       </c>
       <c r="C4" t="n">
-        <v>8802</v>
+        <v>4008</v>
       </c>
       <c r="D4" t="n">
-        <v>8568</v>
+        <v>9807</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1147</v>
+        <v>1720</v>
       </c>
       <c r="C5" t="n">
-        <v>5406</v>
+        <v>2733</v>
       </c>
       <c r="D5" t="n">
-        <v>2604</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>632</v>
+        <v>948</v>
       </c>
       <c r="C6" t="n">
-        <v>3834</v>
+        <v>2392</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>431</v>
       </c>
       <c r="C7" t="n">
-        <v>2240</v>
+        <v>1735</v>
       </c>
       <c r="D7" t="n">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>1084</v>
+        <v>978</v>
       </c>
       <c r="D8" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3491</v>
+        <v>6699</v>
       </c>
       <c r="C2" t="n">
-        <v>5229</v>
+        <v>1694</v>
       </c>
       <c r="D2" t="n">
-        <v>15441</v>
+        <v>21832</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4131</v>
+        <v>7415</v>
       </c>
       <c r="C3" t="n">
-        <v>10229</v>
+        <v>3854</v>
       </c>
       <c r="D3" t="n">
-        <v>15925</v>
+        <v>21054</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2258</v>
+        <v>3611</v>
       </c>
       <c r="C4" t="n">
-        <v>10075</v>
+        <v>4530</v>
       </c>
       <c r="D4" t="n">
-        <v>9586</v>
+        <v>11376</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1277</v>
+        <v>1930</v>
       </c>
       <c r="C5" t="n">
-        <v>6805</v>
+        <v>3333</v>
       </c>
       <c r="D5" t="n">
-        <v>3261</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>735</v>
+        <v>1126</v>
       </c>
       <c r="C6" t="n">
-        <v>4582</v>
+        <v>2632</v>
       </c>
       <c r="D6" t="n">
-        <v>927</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>405</v>
       </c>
       <c r="C7" t="n">
-        <v>2805</v>
+        <v>2067</v>
       </c>
       <c r="D7" t="n">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>1425</v>
+        <v>1248</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3366</v>
+        <v>6814</v>
       </c>
       <c r="C2" t="n">
-        <v>7248</v>
+        <v>6900</v>
       </c>
       <c r="D2" t="n">
-        <v>15154</v>
+        <v>19976</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3264</v>
+        <v>5968</v>
       </c>
       <c r="C3" t="n">
-        <v>7057</v>
+        <v>2480</v>
       </c>
       <c r="D3" t="n">
-        <v>14941</v>
+        <v>19919</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2584</v>
+        <v>4530</v>
       </c>
       <c r="C4" t="n">
-        <v>10034</v>
+        <v>4098</v>
       </c>
       <c r="D4" t="n">
-        <v>10268</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1490</v>
+        <v>2341</v>
       </c>
       <c r="C5" t="n">
-        <v>8107</v>
+        <v>3870</v>
       </c>
       <c r="D5" t="n">
-        <v>4041</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>1339</v>
       </c>
       <c r="C6" t="n">
-        <v>5478</v>
+        <v>2922</v>
       </c>
       <c r="D6" t="n">
-        <v>1250</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>394</v>
+        <v>609</v>
       </c>
       <c r="C7" t="n">
-        <v>3562</v>
+        <v>2335</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="C8" t="n">
-        <v>1965</v>
+        <v>1596</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2037</v>
+        <v>4025</v>
       </c>
       <c r="C2" t="n">
-        <v>3569</v>
+        <v>3173</v>
       </c>
       <c r="D2" t="n">
-        <v>10703</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3202</v>
+        <v>5957</v>
       </c>
       <c r="C3" t="n">
-        <v>6935</v>
+        <v>3921</v>
       </c>
       <c r="D3" t="n">
-        <v>14650</v>
+        <v>19447</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2810</v>
+        <v>5033</v>
       </c>
       <c r="C4" t="n">
-        <v>9902</v>
+        <v>3862</v>
       </c>
       <c r="D4" t="n">
-        <v>10885</v>
+        <v>13432</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1539</v>
+        <v>2432</v>
       </c>
       <c r="C5" t="n">
-        <v>9808</v>
+        <v>4474</v>
       </c>
       <c r="D5" t="n">
-        <v>4145</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>701</v>
+        <v>1119</v>
       </c>
       <c r="C6" t="n">
-        <v>6394</v>
+        <v>3718</v>
       </c>
       <c r="D6" t="n">
-        <v>1215</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>3636</v>
+        <v>2642</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>1359</v>
+        <v>1268</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2415</v>
+        <v>5631</v>
       </c>
       <c r="C2" t="n">
-        <v>7626</v>
+        <v>4744</v>
       </c>
       <c r="D2" t="n">
-        <v>14869</v>
+        <v>12485</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2354</v>
+        <v>4397</v>
       </c>
       <c r="C3" t="n">
-        <v>4899</v>
+        <v>3164</v>
       </c>
       <c r="D3" t="n">
-        <v>13183</v>
+        <v>17372</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2589</v>
+        <v>4731</v>
       </c>
       <c r="C4" t="n">
-        <v>8452</v>
+        <v>3847</v>
       </c>
       <c r="D4" t="n">
-        <v>11132</v>
+        <v>14005</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1809</v>
+        <v>3092</v>
       </c>
       <c r="C5" t="n">
-        <v>9643</v>
+        <v>4141</v>
       </c>
       <c r="D5" t="n">
-        <v>5029</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>912</v>
+        <v>1486</v>
       </c>
       <c r="C6" t="n">
-        <v>7839</v>
+        <v>4046</v>
       </c>
       <c r="D6" t="n">
-        <v>1565</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>420</v>
       </c>
       <c r="C7" t="n">
-        <v>4697</v>
+        <v>3135</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>2166</v>
+        <v>1804</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1660</v>
+        <v>3984</v>
       </c>
       <c r="C2" t="n">
-        <v>4433</v>
+        <v>3337</v>
       </c>
       <c r="D2" t="n">
-        <v>10808</v>
+        <v>9574</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2081</v>
+        <v>4214</v>
       </c>
       <c r="C3" t="n">
-        <v>5384</v>
+        <v>3484</v>
       </c>
       <c r="D3" t="n">
-        <v>12675</v>
+        <v>15940</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2326</v>
+        <v>4262</v>
       </c>
       <c r="C4" t="n">
-        <v>7155</v>
+        <v>3589</v>
       </c>
       <c r="D4" t="n">
-        <v>11156</v>
+        <v>14166</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1928</v>
+        <v>3424</v>
       </c>
       <c r="C5" t="n">
-        <v>9412</v>
+        <v>4064</v>
       </c>
       <c r="D5" t="n">
-        <v>5617</v>
+        <v>7116</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1050</v>
+        <v>1772</v>
       </c>
       <c r="C6" t="n">
-        <v>8676</v>
+        <v>4246</v>
       </c>
       <c r="D6" t="n">
-        <v>1843</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>228</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>5648</v>
+        <v>3589</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>2768</v>
+        <v>2233</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>673</v>
+        <v>766</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2372</v>
+        <v>6756</v>
       </c>
       <c r="C2" t="n">
-        <v>9055</v>
+        <v>6173</v>
       </c>
       <c r="D2" t="n">
-        <v>16333</v>
+        <v>10987</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1634</v>
+        <v>3469</v>
       </c>
       <c r="C3" t="n">
-        <v>4538</v>
+        <v>3060</v>
       </c>
       <c r="D3" t="n">
-        <v>11674</v>
+        <v>14079</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1970</v>
+        <v>3724</v>
       </c>
       <c r="C4" t="n">
-        <v>6240</v>
+        <v>3467</v>
       </c>
       <c r="D4" t="n">
-        <v>11021</v>
+        <v>14007</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1879</v>
+        <v>3390</v>
       </c>
       <c r="C5" t="n">
-        <v>8349</v>
+        <v>3778</v>
       </c>
       <c r="D5" t="n">
-        <v>6083</v>
+        <v>7914</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1234</v>
+        <v>2190</v>
       </c>
       <c r="C6" t="n">
-        <v>8875</v>
+        <v>4135</v>
       </c>
       <c r="D6" t="n">
-        <v>2290</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>414</v>
+        <v>765</v>
       </c>
       <c r="C7" t="n">
-        <v>6769</v>
+        <v>3845</v>
       </c>
       <c r="D7" t="n">
-        <v>832</v>
+        <v>945</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>3698</v>
+        <v>2758</v>
       </c>
       <c r="D8" t="n">
-        <v>424</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1315</v>
+        <v>1276</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5978</v>
+        <v>8370</v>
       </c>
       <c r="C2" t="n">
-        <v>13761</v>
+        <v>11031</v>
       </c>
       <c r="D2" t="n">
-        <v>11219</v>
+        <v>10376</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1751</v>
+        <v>4730</v>
       </c>
       <c r="C2" t="n">
-        <v>5361</v>
+        <v>3407</v>
       </c>
       <c r="D2" t="n">
-        <v>12151</v>
+        <v>8087</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2215</v>
+        <v>4800</v>
       </c>
       <c r="C3" t="n">
-        <v>6011</v>
+        <v>4086</v>
       </c>
       <c r="D3" t="n">
-        <v>12968</v>
+        <v>15025</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2743</v>
+        <v>5006</v>
       </c>
       <c r="C4" t="n">
-        <v>9024</v>
+        <v>4798</v>
       </c>
       <c r="D4" t="n">
-        <v>11252</v>
+        <v>14463</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1140</v>
+        <v>2180</v>
       </c>
       <c r="C5" t="n">
-        <v>12428</v>
+        <v>5699</v>
       </c>
       <c r="D5" t="n">
-        <v>5465</v>
+        <v>7161</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>382</v>
+        <v>706</v>
       </c>
       <c r="C6" t="n">
-        <v>8112</v>
+        <v>4659</v>
       </c>
       <c r="D6" t="n">
-        <v>1817</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>3624</v>
+        <v>2702</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1288</v>
+        <v>1250</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="D9" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6512</v>
+        <v>8487</v>
       </c>
       <c r="C2" t="n">
-        <v>6360</v>
+        <v>7437</v>
       </c>
       <c r="D2" t="n">
-        <v>15510</v>
+        <v>11595</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2540</v>
+        <v>3554</v>
       </c>
       <c r="C3" t="n">
-        <v>6935</v>
+        <v>5559</v>
       </c>
       <c r="D3" t="n">
-        <v>2524</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4735</v>
+        <v>6679</v>
       </c>
       <c r="C2" t="n">
-        <v>10759</v>
+        <v>4245</v>
       </c>
       <c r="D2" t="n">
-        <v>22032</v>
+        <v>22382</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3717</v>
+        <v>4946</v>
       </c>
       <c r="C3" t="n">
-        <v>5700</v>
+        <v>5710</v>
       </c>
       <c r="D3" t="n">
-        <v>4519</v>
+        <v>3754</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1138</v>
+        <v>1578</v>
       </c>
       <c r="C4" t="n">
-        <v>4107</v>
+        <v>3301</v>
       </c>
       <c r="D4" t="n">
-        <v>1690</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="5">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>406</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4269</v>
+        <v>6471</v>
       </c>
       <c r="C2" t="n">
-        <v>7313</v>
+        <v>3445</v>
       </c>
       <c r="D2" t="n">
-        <v>30846</v>
+        <v>25848</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3465</v>
+        <v>4809</v>
       </c>
       <c r="C3" t="n">
-        <v>7290</v>
+        <v>4271</v>
       </c>
       <c r="D3" t="n">
-        <v>6995</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2033</v>
+        <v>2735</v>
       </c>
       <c r="C4" t="n">
-        <v>4908</v>
+        <v>4573</v>
       </c>
       <c r="D4" t="n">
-        <v>2181</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>519</v>
+        <v>695</v>
       </c>
       <c r="C5" t="n">
-        <v>2305</v>
+        <v>1871</v>
       </c>
       <c r="D5" t="n">
-        <v>1251</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
@@ -5221,7 +5221,7 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>371</v>
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5111</v>
+        <v>8118</v>
       </c>
       <c r="C2" t="n">
-        <v>13231</v>
+        <v>4325</v>
       </c>
       <c r="D2" t="n">
-        <v>28875</v>
+        <v>32599</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3165</v>
+        <v>4593</v>
       </c>
       <c r="C3" t="n">
-        <v>6367</v>
+        <v>3360</v>
       </c>
       <c r="D3" t="n">
-        <v>10127</v>
+        <v>8955</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2327</v>
+        <v>3189</v>
       </c>
       <c r="C4" t="n">
-        <v>6063</v>
+        <v>4318</v>
       </c>
       <c r="D4" t="n">
-        <v>2992</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1035</v>
+        <v>1391</v>
       </c>
       <c r="C5" t="n">
-        <v>3581</v>
+        <v>3188</v>
       </c>
       <c r="D5" t="n">
-        <v>1373</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="C6" t="n">
-        <v>1277</v>
+        <v>1083</v>
       </c>
       <c r="D6" t="n">
-        <v>933</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
         <v>471</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6605</v>
+        <v>8881</v>
       </c>
       <c r="C2" t="n">
-        <v>11385</v>
+        <v>4529</v>
       </c>
       <c r="D2" t="n">
-        <v>33645</v>
+        <v>36329</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2967</v>
+        <v>4543</v>
       </c>
       <c r="C3" t="n">
-        <v>7988</v>
+        <v>3151</v>
       </c>
       <c r="D3" t="n">
-        <v>11398</v>
+        <v>11212</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1698</v>
+        <v>2386</v>
       </c>
       <c r="C4" t="n">
-        <v>5040</v>
+        <v>3107</v>
       </c>
       <c r="D4" t="n">
-        <v>3578</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>861</v>
+        <v>1189</v>
       </c>
       <c r="C5" t="n">
-        <v>3533</v>
+        <v>2719</v>
       </c>
       <c r="D5" t="n">
-        <v>1304</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="C6" t="n">
-        <v>1602</v>
+        <v>1429</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>508</v>
+        <v>445</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
         <v>352</v>
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
         <v>272</v>
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5913,10 +5913,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5202</v>
+        <v>7718</v>
       </c>
       <c r="C2" t="n">
-        <v>6150</v>
+        <v>3503</v>
       </c>
       <c r="D2" t="n">
-        <v>24251</v>
+        <v>35923</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3933</v>
+        <v>5552</v>
       </c>
       <c r="C3" t="n">
-        <v>8546</v>
+        <v>3395</v>
       </c>
       <c r="D3" t="n">
-        <v>14296</v>
+        <v>14606</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2027</v>
+        <v>3029</v>
       </c>
       <c r="C4" t="n">
-        <v>6661</v>
+        <v>3068</v>
       </c>
       <c r="D4" t="n">
-        <v>5045</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1122</v>
+        <v>1576</v>
       </c>
       <c r="C5" t="n">
-        <v>4313</v>
+        <v>2859</v>
       </c>
       <c r="D5" t="n">
-        <v>1700</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>534</v>
+        <v>735</v>
       </c>
       <c r="C6" t="n">
-        <v>2624</v>
+        <v>2142</v>
       </c>
       <c r="D6" t="n">
-        <v>837</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>1108</v>
+        <v>994</v>
       </c>
       <c r="D7" t="n">
         <v>557</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>209</v>
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6224,7 +6224,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4291</v>
+        <v>7073</v>
       </c>
       <c r="C2" t="n">
-        <v>4937</v>
+        <v>2554</v>
       </c>
       <c r="D2" t="n">
-        <v>20871</v>
+        <v>35523</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3731</v>
+        <v>5423</v>
       </c>
       <c r="C3" t="n">
-        <v>6365</v>
+        <v>2994</v>
       </c>
       <c r="D3" t="n">
-        <v>14802</v>
+        <v>16965</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2524</v>
+        <v>3638</v>
       </c>
       <c r="C4" t="n">
-        <v>7535</v>
+        <v>3186</v>
       </c>
       <c r="D4" t="n">
-        <v>6579</v>
+        <v>6546</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1357</v>
+        <v>2013</v>
       </c>
       <c r="C5" t="n">
-        <v>5399</v>
+        <v>2911</v>
       </c>
       <c r="D5" t="n">
-        <v>2210</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>742</v>
+        <v>1035</v>
       </c>
       <c r="C6" t="n">
-        <v>3454</v>
+        <v>2468</v>
       </c>
       <c r="D6" t="n">
-        <v>974</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>421</v>
       </c>
       <c r="C7" t="n">
-        <v>1865</v>
+        <v>1589</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>722</v>
+        <v>667</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>

--- a/output/yearly_population_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_11_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7198</v>
+        <v>1375</v>
       </c>
       <c r="C2" t="n">
-        <v>3478</v>
+        <v>2224</v>
       </c>
       <c r="D2" t="n">
-        <v>30617</v>
+        <v>10198</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5133</v>
+        <v>2329</v>
       </c>
       <c r="C3" t="n">
-        <v>2433</v>
+        <v>6131</v>
       </c>
       <c r="D3" t="n">
-        <v>18470</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3799</v>
+        <v>1385</v>
       </c>
       <c r="C4" t="n">
-        <v>2991</v>
+        <v>7626</v>
       </c>
       <c r="D4" t="n">
-        <v>8084</v>
+        <v>5243</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2411</v>
+        <v>590</v>
       </c>
       <c r="C5" t="n">
-        <v>2987</v>
+        <v>4344</v>
       </c>
       <c r="D5" t="n">
-        <v>2821</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1355</v>
+        <v>248</v>
       </c>
       <c r="C6" t="n">
-        <v>2630</v>
+        <v>1406</v>
       </c>
       <c r="D6" t="n">
-        <v>1130</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>619</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>2010</v>
+        <v>511</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1091</v>
+        <v>332</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>443</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10583</v>
+        <v>2210</v>
       </c>
       <c r="C2" t="n">
-        <v>6373</v>
+        <v>5869</v>
       </c>
       <c r="D2" t="n">
-        <v>29979</v>
+        <v>15694</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4941</v>
+        <v>1570</v>
       </c>
       <c r="C3" t="n">
-        <v>2554</v>
+        <v>3462</v>
       </c>
       <c r="D3" t="n">
-        <v>18880</v>
+        <v>9786</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3735</v>
+        <v>1601</v>
       </c>
       <c r="C4" t="n">
-        <v>2637</v>
+        <v>6693</v>
       </c>
       <c r="D4" t="n">
-        <v>9533</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2675</v>
+        <v>847</v>
       </c>
       <c r="C5" t="n">
-        <v>2926</v>
+        <v>6018</v>
       </c>
       <c r="D5" t="n">
-        <v>3516</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1635</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>2736</v>
+        <v>2927</v>
       </c>
       <c r="D6" t="n">
-        <v>1374</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>829</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>2282</v>
+        <v>968</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1467</v>
+        <v>417</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>709</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12475</v>
+        <v>1141</v>
       </c>
       <c r="C2" t="n">
-        <v>4673</v>
+        <v>2340</v>
       </c>
       <c r="D2" t="n">
-        <v>38906</v>
+        <v>10586</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5827</v>
+        <v>1693</v>
       </c>
       <c r="C3" t="n">
-        <v>3642</v>
+        <v>4288</v>
       </c>
       <c r="D3" t="n">
-        <v>19003</v>
+        <v>10276</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3604</v>
+        <v>1754</v>
       </c>
       <c r="C4" t="n">
-        <v>2520</v>
+        <v>5926</v>
       </c>
       <c r="D4" t="n">
-        <v>10497</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2784</v>
+        <v>844</v>
       </c>
       <c r="C5" t="n">
-        <v>2714</v>
+        <v>6953</v>
       </c>
       <c r="D5" t="n">
-        <v>4275</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1862</v>
+        <v>306</v>
       </c>
       <c r="C6" t="n">
-        <v>2789</v>
+        <v>3856</v>
       </c>
       <c r="D6" t="n">
-        <v>1630</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1026</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2441</v>
+        <v>964</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>467</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1771</v>
+        <v>463</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>998</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>449</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>227</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11235</v>
+        <v>930</v>
       </c>
       <c r="C2" t="n">
-        <v>3177</v>
+        <v>4436</v>
       </c>
       <c r="D2" t="n">
-        <v>31854</v>
+        <v>10339</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6794</v>
+        <v>1207</v>
       </c>
       <c r="C3" t="n">
-        <v>5073</v>
+        <v>2855</v>
       </c>
       <c r="D3" t="n">
-        <v>20737</v>
+        <v>9599</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2572</v>
+        <v>1530</v>
       </c>
       <c r="C4" t="n">
-        <v>4008</v>
+        <v>4963</v>
       </c>
       <c r="D4" t="n">
-        <v>9807</v>
+        <v>7105</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1720</v>
+        <v>1118</v>
       </c>
       <c r="C5" t="n">
-        <v>2733</v>
+        <v>6342</v>
       </c>
       <c r="D5" t="n">
-        <v>2746</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>2392</v>
+        <v>5406</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>1735</v>
+        <v>2314</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>978</v>
+        <v>683</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>440</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6699</v>
+        <v>589</v>
       </c>
       <c r="C2" t="n">
-        <v>1694</v>
+        <v>2301</v>
       </c>
       <c r="D2" t="n">
-        <v>21832</v>
+        <v>7066</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7415</v>
+        <v>960</v>
       </c>
       <c r="C3" t="n">
-        <v>3854</v>
+        <v>3251</v>
       </c>
       <c r="D3" t="n">
-        <v>21054</v>
+        <v>9229</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3611</v>
+        <v>1306</v>
       </c>
       <c r="C4" t="n">
-        <v>4530</v>
+        <v>3990</v>
       </c>
       <c r="D4" t="n">
-        <v>11376</v>
+        <v>7340</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1930</v>
+        <v>1214</v>
       </c>
       <c r="C5" t="n">
-        <v>3333</v>
+        <v>5857</v>
       </c>
       <c r="D5" t="n">
-        <v>3596</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1126</v>
+        <v>615</v>
       </c>
       <c r="C6" t="n">
-        <v>2632</v>
+        <v>5977</v>
       </c>
       <c r="D6" t="n">
-        <v>967</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>2067</v>
+        <v>3441</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1248</v>
+        <v>1117</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>490</v>
+        <v>436</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6814</v>
+        <v>1541</v>
       </c>
       <c r="C2" t="n">
-        <v>6900</v>
+        <v>13712</v>
       </c>
       <c r="D2" t="n">
-        <v>19976</v>
+        <v>16514</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5968</v>
+        <v>673</v>
       </c>
       <c r="C3" t="n">
-        <v>2480</v>
+        <v>2473</v>
       </c>
       <c r="D3" t="n">
-        <v>19919</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4530</v>
+        <v>1019</v>
       </c>
       <c r="C4" t="n">
-        <v>4098</v>
+        <v>3538</v>
       </c>
       <c r="D4" t="n">
-        <v>12500</v>
+        <v>7443</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2341</v>
+        <v>1151</v>
       </c>
       <c r="C5" t="n">
-        <v>3870</v>
+        <v>4839</v>
       </c>
       <c r="D5" t="n">
-        <v>4756</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1339</v>
+        <v>790</v>
       </c>
       <c r="C6" t="n">
-        <v>2922</v>
+        <v>5920</v>
       </c>
       <c r="D6" t="n">
-        <v>1357</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>609</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>2335</v>
+        <v>4557</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>801</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>1596</v>
+        <v>2106</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>784</v>
+        <v>711</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4025</v>
+        <v>1023</v>
       </c>
       <c r="C2" t="n">
-        <v>3173</v>
+        <v>6910</v>
       </c>
       <c r="D2" t="n">
-        <v>13800</v>
+        <v>11891</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5957</v>
+        <v>1052</v>
       </c>
       <c r="C3" t="n">
-        <v>3921</v>
+        <v>5981</v>
       </c>
       <c r="D3" t="n">
-        <v>19447</v>
+        <v>9478</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5033</v>
+        <v>1566</v>
       </c>
       <c r="C4" t="n">
-        <v>3862</v>
+        <v>5008</v>
       </c>
       <c r="D4" t="n">
-        <v>13432</v>
+        <v>7845</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2432</v>
+        <v>825</v>
       </c>
       <c r="C5" t="n">
-        <v>4474</v>
+        <v>7719</v>
       </c>
       <c r="D5" t="n">
-        <v>5192</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1119</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>3718</v>
+        <v>6032</v>
       </c>
       <c r="D6" t="n">
-        <v>1320</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>2642</v>
+        <v>2063</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1268</v>
+        <v>696</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5631</v>
+        <v>526</v>
       </c>
       <c r="C2" t="n">
-        <v>4744</v>
+        <v>3567</v>
       </c>
       <c r="D2" t="n">
-        <v>12485</v>
+        <v>8803</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4397</v>
+        <v>881</v>
       </c>
       <c r="C3" t="n">
-        <v>3164</v>
+        <v>5723</v>
       </c>
       <c r="D3" t="n">
-        <v>17372</v>
+        <v>9240</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4731</v>
+        <v>1097</v>
       </c>
       <c r="C4" t="n">
-        <v>3847</v>
+        <v>5194</v>
       </c>
       <c r="D4" t="n">
-        <v>14005</v>
+        <v>7564</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3092</v>
+        <v>809</v>
       </c>
       <c r="C5" t="n">
-        <v>4141</v>
+        <v>5687</v>
       </c>
       <c r="D5" t="n">
-        <v>6299</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1486</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>4046</v>
+        <v>5638</v>
       </c>
       <c r="D6" t="n">
-        <v>1873</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>3135</v>
+        <v>2739</v>
       </c>
       <c r="D7" t="n">
-        <v>670</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1804</v>
+        <v>807</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>647</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>136</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3984</v>
+        <v>550</v>
       </c>
       <c r="C2" t="n">
-        <v>3337</v>
+        <v>6831</v>
       </c>
       <c r="D2" t="n">
-        <v>9574</v>
+        <v>9176</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4214</v>
+        <v>593</v>
       </c>
       <c r="C3" t="n">
-        <v>3484</v>
+        <v>3909</v>
       </c>
       <c r="D3" t="n">
-        <v>15940</v>
+        <v>8504</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4262</v>
+        <v>872</v>
       </c>
       <c r="C4" t="n">
-        <v>3589</v>
+        <v>5440</v>
       </c>
       <c r="D4" t="n">
-        <v>14166</v>
+        <v>7655</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3424</v>
+        <v>848</v>
       </c>
       <c r="C5" t="n">
-        <v>4064</v>
+        <v>5298</v>
       </c>
       <c r="D5" t="n">
-        <v>7116</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1772</v>
+        <v>485</v>
       </c>
       <c r="C6" t="n">
-        <v>4246</v>
+        <v>5654</v>
       </c>
       <c r="D6" t="n">
-        <v>2269</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>3589</v>
+        <v>4242</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>2233</v>
+        <v>1742</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>766</v>
+        <v>519</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6756</v>
+        <v>610</v>
       </c>
       <c r="C2" t="n">
-        <v>6173</v>
+        <v>8035</v>
       </c>
       <c r="D2" t="n">
-        <v>10987</v>
+        <v>15111</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3469</v>
+        <v>480</v>
       </c>
       <c r="C3" t="n">
-        <v>3060</v>
+        <v>4694</v>
       </c>
       <c r="D3" t="n">
-        <v>14079</v>
+        <v>8007</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3724</v>
+        <v>643</v>
       </c>
       <c r="C4" t="n">
-        <v>3467</v>
+        <v>4518</v>
       </c>
       <c r="D4" t="n">
-        <v>14007</v>
+        <v>7577</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3390</v>
+        <v>781</v>
       </c>
       <c r="C5" t="n">
-        <v>3778</v>
+        <v>5260</v>
       </c>
       <c r="D5" t="n">
-        <v>7914</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2190</v>
+        <v>597</v>
       </c>
       <c r="C6" t="n">
-        <v>4135</v>
+        <v>5419</v>
       </c>
       <c r="D6" t="n">
-        <v>2890</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>765</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>3845</v>
+        <v>4918</v>
       </c>
       <c r="D7" t="n">
-        <v>945</v>
+        <v>976</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>2758</v>
+        <v>2892</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1276</v>
+        <v>1058</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8370</v>
+        <v>3126</v>
       </c>
       <c r="C2" t="n">
-        <v>11031</v>
+        <v>3867</v>
       </c>
       <c r="D2" t="n">
-        <v>10376</v>
+        <v>13499</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4730</v>
+        <v>923</v>
       </c>
       <c r="C2" t="n">
-        <v>3407</v>
+        <v>18827</v>
       </c>
       <c r="D2" t="n">
-        <v>8087</v>
+        <v>13731</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4800</v>
+        <v>441</v>
       </c>
       <c r="C3" t="n">
-        <v>4086</v>
+        <v>5467</v>
       </c>
       <c r="D3" t="n">
-        <v>15025</v>
+        <v>8435</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5006</v>
+        <v>496</v>
       </c>
       <c r="C4" t="n">
-        <v>4798</v>
+        <v>4508</v>
       </c>
       <c r="D4" t="n">
-        <v>14463</v>
+        <v>7416</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2180</v>
+        <v>666</v>
       </c>
       <c r="C5" t="n">
-        <v>5699</v>
+        <v>4808</v>
       </c>
       <c r="D5" t="n">
-        <v>7161</v>
+        <v>5195</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>706</v>
+        <v>621</v>
       </c>
       <c r="C6" t="n">
-        <v>4659</v>
+        <v>5243</v>
       </c>
       <c r="D6" t="n">
-        <v>2240</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>362</v>
       </c>
       <c r="C7" t="n">
-        <v>2702</v>
+        <v>5136</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>1250</v>
+        <v>3744</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>1784</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>616</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8487</v>
+        <v>3914</v>
       </c>
       <c r="C2" t="n">
-        <v>7437</v>
+        <v>7787</v>
       </c>
       <c r="D2" t="n">
-        <v>11595</v>
+        <v>17540</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3554</v>
+        <v>1035</v>
       </c>
       <c r="C3" t="n">
-        <v>5559</v>
+        <v>1527</v>
       </c>
       <c r="D3" t="n">
-        <v>2382</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6679</v>
+        <v>2808</v>
       </c>
       <c r="C2" t="n">
-        <v>4245</v>
+        <v>7522</v>
       </c>
       <c r="D2" t="n">
-        <v>22382</v>
+        <v>13794</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4946</v>
+        <v>2096</v>
       </c>
       <c r="C3" t="n">
-        <v>5710</v>
+        <v>4562</v>
       </c>
       <c r="D3" t="n">
-        <v>3754</v>
+        <v>4925</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1578</v>
+        <v>505</v>
       </c>
       <c r="C4" t="n">
-        <v>3301</v>
+        <v>1000</v>
       </c>
       <c r="D4" t="n">
-        <v>1661</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6471</v>
+        <v>2671</v>
       </c>
       <c r="C2" t="n">
-        <v>3445</v>
+        <v>6363</v>
       </c>
       <c r="D2" t="n">
-        <v>25848</v>
+        <v>13450</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4809</v>
+        <v>2047</v>
       </c>
       <c r="C3" t="n">
-        <v>4271</v>
+        <v>5411</v>
       </c>
       <c r="D3" t="n">
-        <v>6464</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2735</v>
+        <v>1139</v>
       </c>
       <c r="C4" t="n">
-        <v>4573</v>
+        <v>3133</v>
       </c>
       <c r="D4" t="n">
-        <v>2012</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>695</v>
+        <v>265</v>
       </c>
       <c r="C5" t="n">
-        <v>1871</v>
+        <v>666</v>
       </c>
       <c r="D5" t="n">
-        <v>1234</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8118</v>
+        <v>2280</v>
       </c>
       <c r="C2" t="n">
-        <v>4325</v>
+        <v>5263</v>
       </c>
       <c r="D2" t="n">
-        <v>32599</v>
+        <v>18927</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4593</v>
+        <v>1940</v>
       </c>
       <c r="C3" t="n">
-        <v>3360</v>
+        <v>5182</v>
       </c>
       <c r="D3" t="n">
-        <v>8955</v>
+        <v>6907</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3189</v>
+        <v>1366</v>
       </c>
       <c r="C4" t="n">
-        <v>4318</v>
+        <v>4349</v>
       </c>
       <c r="D4" t="n">
-        <v>2762</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1391</v>
+        <v>605</v>
       </c>
       <c r="C5" t="n">
-        <v>3188</v>
+        <v>2049</v>
       </c>
       <c r="D5" t="n">
-        <v>1319</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>354</v>
+        <v>171</v>
       </c>
       <c r="C6" t="n">
-        <v>1083</v>
+        <v>478</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8881</v>
+        <v>2976</v>
       </c>
       <c r="C2" t="n">
-        <v>4529</v>
+        <v>7484</v>
       </c>
       <c r="D2" t="n">
-        <v>36329</v>
+        <v>21535</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4543</v>
+        <v>1735</v>
       </c>
       <c r="C3" t="n">
-        <v>3151</v>
+        <v>4531</v>
       </c>
       <c r="D3" t="n">
-        <v>11212</v>
+        <v>8332</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2386</v>
+        <v>1421</v>
       </c>
       <c r="C4" t="n">
-        <v>3107</v>
+        <v>4722</v>
       </c>
       <c r="D4" t="n">
-        <v>3323</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1189</v>
+        <v>842</v>
       </c>
       <c r="C5" t="n">
-        <v>2719</v>
+        <v>3242</v>
       </c>
       <c r="D5" t="n">
-        <v>1227</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="C6" t="n">
-        <v>1429</v>
+        <v>1287</v>
       </c>
       <c r="D6" t="n">
-        <v>771</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>445</v>
+        <v>386</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7718</v>
+        <v>3274</v>
       </c>
       <c r="C2" t="n">
-        <v>3503</v>
+        <v>9179</v>
       </c>
       <c r="D2" t="n">
-        <v>35923</v>
+        <v>18143</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5552</v>
+        <v>1884</v>
       </c>
       <c r="C3" t="n">
-        <v>3395</v>
+        <v>5233</v>
       </c>
       <c r="D3" t="n">
-        <v>14606</v>
+        <v>9659</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3029</v>
+        <v>1343</v>
       </c>
       <c r="C4" t="n">
-        <v>3068</v>
+        <v>4479</v>
       </c>
       <c r="D4" t="n">
-        <v>4812</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1576</v>
+        <v>983</v>
       </c>
       <c r="C5" t="n">
-        <v>2859</v>
+        <v>3927</v>
       </c>
       <c r="D5" t="n">
-        <v>1580</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>735</v>
+        <v>512</v>
       </c>
       <c r="C6" t="n">
-        <v>2142</v>
+        <v>2230</v>
       </c>
       <c r="D6" t="n">
-        <v>847</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="C7" t="n">
-        <v>994</v>
+        <v>818</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7073</v>
+        <v>2892</v>
       </c>
       <c r="C2" t="n">
-        <v>2554</v>
+        <v>5507</v>
       </c>
       <c r="D2" t="n">
-        <v>35523</v>
+        <v>14171</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5423</v>
+        <v>2476</v>
       </c>
       <c r="C3" t="n">
-        <v>2994</v>
+        <v>8278</v>
       </c>
       <c r="D3" t="n">
-        <v>16965</v>
+        <v>10753</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3638</v>
+        <v>908</v>
       </c>
       <c r="C4" t="n">
-        <v>3186</v>
+        <v>6650</v>
       </c>
       <c r="D4" t="n">
-        <v>6546</v>
+        <v>4149</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2013</v>
+        <v>473</v>
       </c>
       <c r="C5" t="n">
-        <v>2911</v>
+        <v>2185</v>
       </c>
       <c r="D5" t="n">
-        <v>2121</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1035</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>2468</v>
+        <v>801</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>646</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>1589</v>
+        <v>330</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>667</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
         <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
